--- a/Result/checksun_type/冷凍空調設備及零件.xlsx
+++ b/Result/checksun_type/冷凍空調設備及零件.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>43.34</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>44.54</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>44.1</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>44.1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>4853.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4429.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4429.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>6673.8</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>11856.62</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>11856.62</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-1624.068372518221</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>4853</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>4853.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>43.17</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>44.59</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>44.12</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>44.59</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>44.12</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>1691.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4940.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>4940.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>7994.1</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>12738.84</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>12738.84</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-1744.419607382416</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>1691</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>1691.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>43.3</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>44.63</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>44.15</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>44.63</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>44.15</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>3181.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>5627.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>5627.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>8454.3</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>12850.78</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>12850.78</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1515.263528353322</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>3181</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>3181.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>43.75000000000001</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>44.72</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>44.17</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>44.17</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>4969.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>7013.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>7013.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>8677.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>12968.26</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>12968.26</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-1293.42400372771</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>4969</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>4969.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>44.18</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>44.79</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>44.2</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>44.79</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>44.2</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>7452.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>7629.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>7629</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>9121.5</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>13002.5</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>13002.5</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-1121.888111272277</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>7452</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>7452.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>44.56</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>44.82</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>44.22</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>44.82</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>44.22</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>7411.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>8918.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>8918.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>9112.0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>12973.78</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>12973.78</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-1102.80511807622</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>7411</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>7411.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>45.15</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>44.91</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>44.27</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>44.91</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>44.27</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>5124.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>11047.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>11047.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>9783.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>12989.6</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>12989.6</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-1031.764945007699</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>5124</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>5124.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>45.33</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>44.95</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>44.29</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>44.95</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>44.29</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>10110.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>11281.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>11281.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>10487.6</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>13046.46</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>13046.46</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-648.3945211595383</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>10110</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>10110.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>45.07000000000001</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>44.85</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>44.29</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>44.85</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>44.29</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>8048.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>10342.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>10342.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>11090.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>12991.58</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>12991.58</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-611.7798256207552</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>8048</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>8048.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>44.92999999999999</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>44.74</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>44.29</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>44.74</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>44.29</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>13899.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>10614.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>10614</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>12592.3</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>13193.24</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>13193.24</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-316.6952667931801</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>13899</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>13899.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>44.70999999999999</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>44.57</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>44.3</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>44.57</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>44.3</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>18056.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>9305.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>9305.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>15140.7</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>13329.78</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>13329.78</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-510.7282089397449</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>18056</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>18056.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>661.0</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>693.85</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>757.74</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>693.85</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>757.74</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>712958.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>792037.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>792037</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>1109041.5</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1587746.18</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1587746.18</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-180463.9620508341</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>712958</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>712958.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>661.2</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>698.65</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>763.12</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>698.65</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>763.12</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>625808.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>1047539.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>1047539.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>1197029.2</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1609718.98</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1609718.98</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-173323.4371483272</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>625808</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>625808.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>654.4</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>701.8</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>768.9</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>701.8</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>768.9</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>643959.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>1163874.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>1163874.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>1469582.0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1641057.24</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1641057.24</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-147595.0645323058</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>643959</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>643959.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>657.6</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>705.65</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>775.68</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>705.65</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>775.6799999999999</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>706601.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>1264658.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>1264658.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>1638238.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1667740.04</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1667740.04</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-107513.7442046928</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>706601</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>706601.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>657.8</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>709.9</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>781.92</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>781.92</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>1270859.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>1337944.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>1337944.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>1646579.6</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1693766.7</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1693766.7</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-53126.58144364925</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>1270859</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>1270859.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>659.8</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>713.75</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>787.68</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>713.75</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>787.6799999999999</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>1990469.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>1426046.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>1426046</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>1661220.1</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1766700.72</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1766700.72</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-33989.47101917118</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>1990469</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>1990469.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>653.2</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>720.2</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>792.16</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>720.2</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>792.16</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>1207486.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>1346519.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>1346519.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1548234.4</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1812003.46</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1812003.46</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-82537.90359066054</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>1207486</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1207486.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>655.4</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>728.45</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>796.64</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>728.45</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>796.64</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>1147878.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>1775289.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>1775289.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>1535904.2</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1855325.14</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1855325.14</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-65053.98927883594</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>1147878</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>1147878.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>659.0</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>736.75</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>802.06</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>736.75</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>802.0599999999999</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>1073032.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>2011819.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>2011819.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1515893.9</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>1946359.3</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>1946359.3</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-31367.04064484267</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>1073032</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>1073032.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>679.8</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>747.95</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>808.66</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>747.95</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>808.66</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>1711365.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>1955214.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>1955214.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1550532.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>2038998.2</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>2038998.2</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>25896.6374267491</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>1711365</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1711365.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>694.0</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>757.8</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>812.84</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>757.8</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>812.84</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>1592835.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>1896394.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>1896394.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1630314.3</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>2070739.62</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>2070739.62</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>38384.19047806808</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>1592835</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>1592835.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>22.78</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>22.68</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>23.25</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>23.25</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>9458.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>3388.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>3388.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>2604.9</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>2869.44</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>2869.44</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>366.1223336369967</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>9458</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>9458.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>22.38</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>23.25</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>23.25</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>1482.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>2005.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>2005.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>2493.7</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>2744.18</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>2744.18</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-206.215010213768</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>1482</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>1482.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>22.37</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>22.62</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>23.31</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>23.31</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>1564.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>1993.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>1993.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>2593.6</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>2767.54</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>2767.54</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-161.9035367786546</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>1564</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>1564.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>22.43</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>22.64</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>23.37</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>23.37</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>3759.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>1965.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>1965.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>3319.5</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>2794.42</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>2794.42</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-101.6048769863974</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>3759</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>3759.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>22.66</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>23.44</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>22.66</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>23.44</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>680.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>1478.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>1478.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>3093.5</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>2764.8</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>2764.8</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-247.0137602479449</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>680</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>680.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>22.86</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>22.68</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>23.52</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>23.52</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>2542.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>1821.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>1821.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>3254.9</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>2867.44</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>2867.44</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-116.0259591841573</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>2542</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>2542.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>23.14</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>22.72</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>23.61</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>22.72</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>23.61</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>1423.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>2982.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>2982</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>3146.0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>3156.52</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>3156.52</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-124.2567448364548</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>1423</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>1423.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>23.29</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>23.65</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>23.65</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>1425.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>3193.6</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>3193.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>3280.0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>3195.24</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>3195.24</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-11.68441202414942</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>1425</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>1425.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>23.36</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>22.77</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>23.68</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>23.68</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>1322.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>4673.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>4673.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>3200.6</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>3233.78</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>3233.78</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>149.3362209942916</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>1322</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>1322.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>23.02</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>22.78</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>23.72</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>23.72</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>2394.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>4708.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>4708.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>3208.6</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>3272.1</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>3272.1</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>385.0679745565544</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>2394</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>2394.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>22.72</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>22.76</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>23.77</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>22.76</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>23.77</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>8346.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>4688.6</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>4688.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>3120.8</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>3253.26</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>3253.26</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>593.2180519827671</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>8346</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>8346.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>23.44</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>23.08</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>23.64</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>23.64</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>28651594.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>26412037.4</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>26412037.4</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>30286627.2</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>35165862.54</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>35165862.54</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-1995234.31145836</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>28651594</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>28651594.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>23.16</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>23.06</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>23.63</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>23.63</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>21583832.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>27557734.8</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>27557734.8</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>40524896.6</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>35803552.26</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>35803552.26</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-2150215.843458254</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>21583832</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>21583832.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>23.06</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>23.04</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>23.63</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>23.04</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>23.63</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>22181528.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>28135320.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>28135320.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>39633917.6</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>36011463.38</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>36011463.38</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-1537564.394763168</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>22181528</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>22181528.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>22.99</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>23.04</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>23.63</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>23.04</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>23.63</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>34368123.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>31216081.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>31216081.6</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>40715577.2</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>36823717.52</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>36823717.52</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-671473.8825286403</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>34368123</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>34368123.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>23.03</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>23.06</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>23.65</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>23.65</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>25275110.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>31834003.2</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>31834003.2</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>38890051.2</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>36498342.5</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>36498342.5</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-715927.119246155</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>25275110</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>25275110.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>23.19</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>23.1</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>23.68</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>23.68</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>34380081.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>34161217.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>34161217</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>37442490.7</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>36360141.5</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>36360141.5</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>220388.4754161909</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>34380081</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>34380081.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>23.46</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>23.16</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>23.71</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>23.71</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>24471761.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>53492058.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>53492058.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>36779130.0</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>36349246.34</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>36349246.34</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>574578.5579546764</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>24471761</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>24471761.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>23.36</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>23.73</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>23.73</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>37585333.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>51132514.6</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>51132514.6</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>38407665.8</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>36241312.54</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>36241312.54</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>2121649.441654138</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>37585333</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>37585333.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>23.2</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>23.25</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>23.74</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>23.74</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>37457731.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>50215072.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>50215072.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>37782967.8</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>36363555.64</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>36363555.64</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>2850951.938308574</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>37457731</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>37457731.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>23.11</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>23.29</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>23.76</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>23.76</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>36911179.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>45946099.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>45946099.2</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>36138577.6</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>36191151.76</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>36191151.76</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>3804664.578589596</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>36911179</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>36911179.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>22.91</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>23.3</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>23.77</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>23.77</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>131034288.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>40723764.4</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>40723764.4</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>35494782.3</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>37237813.42</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>37237813.42</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>5089789.472612858</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>131034288</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>131034288.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>39.02</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>39.02</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>39.07</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>39.07</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>1046.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>857.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>857.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>918.5</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>1721.18</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>1721.18</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-40.42351111232063</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>1046</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>1046.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>38.97</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>39.01</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>39.05</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>39.01</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>39.05</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>1211.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>922.0</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>922</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>867.2</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>1723.32</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>1723.32</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-57.00306426172483</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>1211</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>1211.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>38.95</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>39.01</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>39.03</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>39.01</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>39.03</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>657.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>908.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>908.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>953.3</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>1838.88</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>1838.88</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-96.33088789438364</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>657</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>657.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>38.97</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>39.02</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>39.02</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>39.02</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>593.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>949.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>949.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>948.2</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>1845.76</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>1845.76</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-89.71596137338236</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>593</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>593.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>39.0</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>39.05</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>39.03</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>39.03</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>782.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>984.6</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>984.6</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>925.2</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>1870.9</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>1870.9</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-70.20478200861692</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>782</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>782.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>39.07</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>39.06</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>39.04</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>39.06</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>39.04</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>1367.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>979.2</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>979.2</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>882.3</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>1875.04</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>1875.04</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-60.07435498721566</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>1367</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>1367.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>39.21</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>39.09</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>39.05</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>39.09</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>39.05</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>1143.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>812.4</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>812.4</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>797.5</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>1854.54</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>1854.54</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-106.1353751356705</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>1143</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>1143.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>39.17</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>39.09</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>39.05</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>39.09</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>39.05</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>864.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>998.2</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>998.2</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>792.3</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>1834.84</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>1834.84</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-144.1462833786177</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>864</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>864.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>39.16</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>39.09</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>39.04</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>39.09</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>39.04</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>767.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>946.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>946.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>879.7</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>1838.84</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>1838.84</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-163.4066421764485</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>767</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>767.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>39.28</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>39.08</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>39.04</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>39.08</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>39.04</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>755.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>865.8</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>865.8</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>845.8</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>1854.92</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>1854.92</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-174.6926318099054</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>755</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>755.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>39.22</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>39.02</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>39.06</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>39.06</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>533.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>785.4</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>785.4</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>848.5</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>1853.94</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>1853.94</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-183.2907372930614</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>533</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>533.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>28.63</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>32.3</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>33.12</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>33.12</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>8443.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>10671.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>10671.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>12990.8</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>12896.28</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>12896.28</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-3031.704124556056</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>8443</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>8443.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>32.56</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>33.2</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>33.2</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>9235.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>10227.4</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>10227.4</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>16695.2</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>12818.96</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>12818.96</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-2796.460876558825</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>9235</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>9235.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>28.28</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>33.3</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>33.3</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>15424.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>12820.6</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>12820.6</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>20899.3</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>12667.5</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>12667.5</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-2445.38263382854</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>15424</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>15424.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>28.58</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>33.09</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>33.09</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>33.4</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>9120.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>13542.0</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>13542</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>23919.9</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>12421.88</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>12421.88</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-2519.614335862825</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>9120</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>9120.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>28.7</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>33.39</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>33.52</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>33.39</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>33.52</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>11137.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>14252.0</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>14252</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>28881.1</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>12304.72</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>12304.72</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-1860.244826773847</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>11137</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>11137.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>29.08</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>33.65</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>33.63</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>33.65</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>33.63</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>6221.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>15309.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>15309.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>32816.3</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>12126.28</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>12126.28</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-1067.958212833386</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>6221</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>6221.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>29.58</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>33.92</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>33.75</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>33.92</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>33.75</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>22201.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>23163.0</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>23163</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>34439.3</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>12067.88</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>12067.88</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>628.7354575398967</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>22201</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>22201.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>30.31</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>34.18</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>33.86</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>34.18</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>33.86</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>19031.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>28978.0</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>28978</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>42162.6</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>11654.98</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>11654.98</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>1317.985863161019</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>19031</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>19031.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>31.42</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>34.35</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>33.94</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>33.94</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>12670.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>34297.8</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>34297.8</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>41747.8</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>11323.66</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>11323.66</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>2595.201233221156</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>12670</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>12670.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>33.57</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>34.6</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>34.04</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>34.04</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>16426.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>43510.2</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>43510.2</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>41320.9</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>11148.8</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>11148.8</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>5008.644574977741</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>16426</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>16426.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>35.53</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>34.76</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>34.12</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>34.76</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>34.12</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>45487.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>50322.8</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>50322.8</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>40533.5</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>10930.88</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>10930.88</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>7875.112042666522</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>45487</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>45487.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29647,11 +29251,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
           <t>2459</t>
@@ -29833,41 +29433,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
+      <c r="AM68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO68" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr">
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT68" t="inlineStr">
         <is>
           <t>0</t>
@@ -29888,20 +29484,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>0</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>0</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29510,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>0</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29679,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29863,11 @@
           <t>32.36</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>33.57</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>36.62</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>36.62</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29914,16 @@
           <t>403535423.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>568945866.2</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>568945866.2</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>551325175.1</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>652100733.04</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>652100733.04</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29940,10 @@
           <t>-64629376.5640012</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>403535423</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>403535423.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30109,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30293,11 @@
           <t>32.41</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>33.75</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>36.78</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>36.78</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30344,16 @@
           <t>363440217.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>575528949.6</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>575528949.6</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>594264436.4</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>657290966.96</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>657290966.96</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30370,10 @@
           <t>-58722927.5542357</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>363440217</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>363440217.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30539,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30723,11 @@
           <t>32.3</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>33.94</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>36.93</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>36.93</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30774,16 @@
           <t>451484020.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>575978704.8</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>575978704.8</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>641378457.8</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>656768454.26</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>656768454.26</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30800,10 @@
           <t>-43891980.91334808</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>451484020</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>451484020.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30969,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31153,11 @@
           <t>32.09</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>34.14</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>37.07</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>37.07</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31204,16 @@
           <t>569640781.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>620997783.6</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>620997783.6</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>705807978.8</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>655783883.94</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>655783883.9400001</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31230,10 @@
           <t>-30570608.14374614</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>569640781</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>569640781.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31399,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31583,11 @@
           <t>32.14</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>34.4</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>37.2</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31634,16 @@
           <t>1056628890.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>631631786.8</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>631631786.8</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>709807982.0</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>651233510.34</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>651233510.34</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31660,10 @@
           <t>-23107921.14632392</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>1056628890</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>1056628890.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31829,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32013,11 @@
           <t>32.12</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>34.62</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>37.31</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>37.31</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32064,16 @@
           <t>436450840.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>533704484.0</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>533704484</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>667262298.9</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>638216857.76</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>638216857.76</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32090,10 @@
           <t>-63798954.21620893</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>436450840</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>436450840.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32259,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32443,11 @@
           <t>32.35</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>37.46</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>37.46</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32494,16 @@
           <t>365688993.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>612999923.2</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>612999923.2</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>705359369.1</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>635887126.76</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>635887126.76</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32520,10 @@
           <t>-53202819.16546595</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>365688993</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>365688993.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32689,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32873,11 @@
           <t>32.81</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>35.28</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>37.61</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>37.61</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32924,16 @@
           <t>676579414.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>706778210.8</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>706778210.8</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>768838281.6</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>633235828.68</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>633235828.6799999</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32950,10 @@
           <t>-28583756.22992349</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>676579414</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>676579414.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33119,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33303,11 @@
           <t>33.39</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>35.56</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>37.76</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>37.76</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33354,16 @@
           <t>622810797.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>790618174.0</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>790618174</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>763691422.1</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>627286041.56</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>627286041.5599999</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33380,10 @@
           <t>-25702505.84950864</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>622810797</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>622810797.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33549,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33733,11 @@
           <t>34.07</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>35.84</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>37.9</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33784,16 @@
           <t>566992376.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>787984177.2</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>787984177.2</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>817890552.4</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>622376486.36</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>622376486.36</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33810,10 @@
           <t>-14907563.99000478</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>566992376</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>566992376.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33979,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34163,11 @@
           <t>34.47</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>38.03</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>38.03</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34214,16 @@
           <t>832928036.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>800820113.8</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>800820113.8</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>848956198.4</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>625070436.22</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>625070436.22</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34240,10 @@
           <t>7026739.630357981</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>832928036</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>832928036.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34409,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34593,11 @@
           <t>34.14</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>34.28</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>35.67</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>34.28</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>35.67</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34644,16 @@
           <t>703729.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>832338.4</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>832338.4</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>1365486.3</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>2770195.72</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>2770195.72</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34670,10 @@
           <t>-407242.1677682393</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>703729</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>703729.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34839,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35023,11 @@
           <t>34.05</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>34.34</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>35.73</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>35.73</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35074,16 @@
           <t>811272.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>1025107.0</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>1025107</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>1422951.5</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>2781982.36</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>2781982.36</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35100,10 @@
           <t>-397836.2898797004</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>811272</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>811272.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35269,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35453,11 @@
           <t>33.98</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>34.42</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>35.78</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>34.42</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>35.78</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35504,16 @@
           <t>1487179.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>1339575.6</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>1339575.6</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>1890505.4</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>2785701.92</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>2785701.92</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35530,10 @@
           <t>-381713.3468289413</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>1487179</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>1487179.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35699,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35883,11 @@
           <t>33.97</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>34.5</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>35.84</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>35.84</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35934,16 @@
           <t>582054.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>1655590.0</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>1655590</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>2092838.2</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>2769787.1</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>2769787.1</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35960,10 @@
           <t>-417466.5586553942</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>582054</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>582054.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36129,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36313,11 @@
           <t>33.92999999999999</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>34.57</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>35.9</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>34.57</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>35.9</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36364,16 @@
           <t>577458.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>1688519.2</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>1688519.2</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>2334206.6</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>2765629.48</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>2765629.48</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36390,10 @@
           <t>-356655.3770269202</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>577458</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>577458.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36559,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36743,11 @@
           <t>33.93</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>34.66</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>35.97</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>35.97</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36794,16 @@
           <t>1667572.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>1898634.2</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>1898634.2</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>2466923.8</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>2771121.32</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>2771121.32</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36820,10 @@
           <t>-256552.1398067102</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>1667572</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>1667572.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36989,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37173,11 @@
           <t>33.97</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>34.74</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>36.03</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>34.74</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>36.03</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37224,16 @@
           <t>2383615.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>1820796.0</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>1820796</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>2506266.8</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>2754839.88</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>2754839.88</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37250,10 @@
           <t>-221182.8673561704</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>2383615</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>2383615.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37419,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37603,11 @@
           <t>33.98999999999999</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>34.83</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>36.09</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37654,16 @@
           <t>3067251.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>2441435.2</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>2441435.2</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>2486763.3</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>2745284.78</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>2745284.78</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37680,10 @@
           <t>-239474.8400212508</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>3067251</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>3067251.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37849,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38033,11 @@
           <t>33.98999999999999</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>34.92</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>36.15</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>36.15</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38084,16 @@
           <t>746700.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>2530086.4</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>2530086.4</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>2848651.5</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>2788241.7</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>2788241.7</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38110,10 @@
           <t>-330300.2709706062</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>746700</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>746700.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38279,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38463,11 @@
           <t>34.08</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>35.03</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>35.03</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>36.21</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38514,16 @@
           <t>1628033.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>2979894.0</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>2979894</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>3115544.6</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>2857333.8</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>2857333.8</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38540,10 @@
           <t>-199623.9840778778</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>1628033</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>1628033.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38709,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38893,11 @@
           <t>34.17</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>35.12</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>36.27</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>36.27</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38944,16 @@
           <t>1278381.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>3035213.4</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>3035213.4</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>3208352.2</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>2902801.48</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>2902801.48</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38970,10 @@
           <t>-100242.6819426282</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>1278381</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>1278381.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39139,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39323,11 @@
           <t>150.6</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>149.25</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>153.56</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>149.25</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>153.56</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39374,16 @@
           <t>467298154.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>1091975503.2</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>1091975503.2</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>971699108.1</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>769361530.6</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>769361530.6</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39400,10 @@
           <t>-15119773.40763056</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>467298154</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>467298154.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39569,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39753,11 @@
           <t>150.6</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>149.15</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>153.79</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>149.15</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>153.79</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39804,16 @@
           <t>710824368.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>1337624644.6</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>1337624644.6</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>951778434.3</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>775873277.4</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>775873277.4</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39830,10 @@
           <t>31499619.18289268</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>710824368</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>710824368.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +39999,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40183,11 @@
           <t>150.2</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>149.18</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>154.09</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>149.18</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>154.09</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40234,16 @@
           <t>984361332.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>1371944247.6</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>1371944247.6</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>917139763.8</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>770428376.1</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>770428376.1</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40260,10 @@
           <t>70881670.69853663</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>984361332</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>984361332.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40429,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40613,11 @@
           <t>148.9</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>149.2</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>154.33</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>149.2</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>154.33</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40664,16 @@
           <t>1286525950.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>1232573788.2</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>1232573788.2</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>862961176.8</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>763733625.74</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>763733625.74</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40690,10 @@
           <t>95302724.1959374</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>1286525950</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>1286525950.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40859,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41043,11 @@
           <t>147.8</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>149.2</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>154.58</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>149.2</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>154.58</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41094,16 @@
           <t>2010867712.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>1072694303.0</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>1072694303</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>856900855.0</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>752922533.34</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>752922533.34</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41120,10 @@
           <t>94411494.2566551</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>2010867712</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>2010867712.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41289,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41473,11 @@
           <t>147.6</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>149.32</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>154.87</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>149.32</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>154.87</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41524,16 @@
           <t>1695543861.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>851422713.0</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>851422713</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>685544317.2</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>751668929.8</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>751668929.8</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41550,10 @@
           <t>12158423.61994255</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>1695543861</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>1695543861.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41719,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41903,11 @@
           <t>146.3</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>149.52</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>155.2</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>149.52</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>155.2</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41954,16 @@
           <t>882422383.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>565932224.0</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>565932224</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>581506824.1</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>740084780.12</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>740084780.12</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41980,10 @@
           <t>-71995494.09750187</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>882422383</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>882422383.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42149,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42333,11 @@
           <t>145.7</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>149.88</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>155.56</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>149.88</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>155.56</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42384,16 @@
           <t>287509035.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>462335280.0</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>462335280</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>605251513.7</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>735380608.92</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>735380608.92</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42410,10 @@
           <t>-102523950.5475115</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>287509035</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>287509035.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42579,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42763,11 @@
           <t>145.6</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>150.48</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>155.9</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>150.48</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>155.9</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42814,16 @@
           <t>487128524.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>493348565.4</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>493348565.4</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>870934906.4</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>755782564.6</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>755782564.6</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42840,10 @@
           <t>-78733745.67082834</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>487128524</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>487128524.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43009,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43193,11 @@
           <t>145.4</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>151.1</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>156.28</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>151.1</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>156.28</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43244,16 @@
           <t>904509762.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>641107407.0</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>641107407</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>1218580183.3</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>785438747.86</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>785438747.86</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43270,10 @@
           <t>-63323621.60875154</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>904509762</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>904509762.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43439,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43623,11 @@
           <t>145.6</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>151.43</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>156.71</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>151.43</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>156.71</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43674,16 @@
           <t>268091416.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>519665921.4</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>519665921.4</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>1219128474.1</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>811875622.62</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>811875622.62</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43700,10 @@
           <t>-83767019.10547185</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>268091416</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>268091416.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43869,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44053,11 @@
           <t>11.66</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>12.59</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>12.59</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44104,16 @@
           <t>1689808.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>1722090.2</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>1722090.2</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>1468126.6</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>2132319.7</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>2132319.7</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44130,10 @@
           <t>4240.355987737188</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>1689808</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>1689808.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44299,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44483,11 @@
           <t>11.67</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>12.02</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>12.63</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>12.63</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44534,16 @@
           <t>1284433.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>1652531.6</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>1652531.6</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>1560047.5</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>2184135.08</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>2184135.08</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44560,10 @@
           <t>-8836.885795826325</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>1284433</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>1284433.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44729,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44913,11 @@
           <t>11.72</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>12.06</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>12.68</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>12.68</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44964,16 @@
           <t>1802947.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>1713009.6</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>1713009.6</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>1513530.8</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>2247345.76</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>2247345.76</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44990,10 @@
           <t>16229.9790060767</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>1802947</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>1802947.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45159,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45343,11 @@
           <t>11.81</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>12.11</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>12.73</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>12.73</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45394,16 @@
           <t>1790473.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>1419144.0</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>1419144</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>1372055.4</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>2310821.12</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>2310821.12</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45420,10 @@
           <t>-4094.927669993136</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>1790473</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>1790473.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45589,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45773,11 @@
           <t>11.9</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>12.16</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>12.79</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>12.79</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45824,16 @@
           <t>2042790.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>1351908.0</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>1351908</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>1497639.3</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>2474783.38</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>2474783.38</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45850,10 @@
           <t>-31647.76121902163</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>2042790</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>2042790.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46019,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46203,11 @@
           <t>11.98</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>12.83</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>12.83</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46254,16 @@
           <t>1342015.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>1214163.0</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>1214163</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>1421321.6</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>2495604.78</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>2495604.78</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46280,10 @@
           <t>-96912.6391026685</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>1342015</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>1342015.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46449,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46633,11 @@
           <t>12.1</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>12.24</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>12.88</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>12.88</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46684,16 @@
           <t>1586823.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>1467563.4</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>1467563.4</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>1378485.3</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>2574584.24</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>2574584.24</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46710,10 @@
           <t>-111603.9775399261</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>1586823</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>1586823.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46879,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47063,11 @@
           <t>12.16</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>12.29</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>12.92</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>12.92</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47114,16 @@
           <t>333619.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>1314052.0</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>1314052</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>1255015.7</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>2652183.68</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>2652183.68</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47140,10 @@
           <t>-154835.1761095824</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>333619</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>333619.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47309,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47493,11 @@
           <t>12.17</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>12.33</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>12.96</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>12.96</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47544,16 @@
           <t>1454293.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>1324966.8</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>1324966.8</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>1306535.7</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>2739028.94</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>2739028.94</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47570,10 @@
           <t>-76792.34634803515</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>1454293</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>1454293.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47739,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47923,11 @@
           <t>12.23</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>12.37</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>13.01</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>13.01</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47974,16 @@
           <t>1354065.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>1643370.6</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>1643370.6</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>1313687.1</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>2963261.74</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>2963261.74</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48000,10 @@
           <t>-82632.22003339487</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>1354065</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>1354065.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48169,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48353,11 @@
           <t>12.22</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>12.41</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>13.05</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>13.05</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48404,16 @@
           <t>2609017.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>1628480.2</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>1628480.2</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>1449915.1</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>3215446.22</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>3215446.22</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48430,10 @@
           <t>-77285.03172557289</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>2609017</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>2609017.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48599,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48783,11 @@
           <t>91.34</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>103.07</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>103.31</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>103.07</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>103.31</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48834,16 @@
           <t>2683545818.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>5000685349.4</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>5000685349.4</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>4727097624.7</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>6863428946.3</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>6863428946.3</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48860,10 @@
           <t>-78239912.41163445</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>2683545818</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>2683545818.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49029,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49213,11 @@
           <t>92.5</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>104.44</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>103.43</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>104.44</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>103.43</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49264,16 @@
           <t>4682266073.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>5019578044.4</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>5019578044.4</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>4597307742.4</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>7180754379.14</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>7180754379.14</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49290,10 @@
           <t>116188863.3358154</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>4682266073</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>4682266073.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49459,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49643,11 @@
           <t>93.56</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>105.81</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>103.41</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>105.81</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>103.41</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49694,16 @@
           <t>11515775721.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>4696916791.4</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>4696916791.4</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>4341077616.0</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>7241408797.74</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>7241408797.74</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49720,10 @@
           <t>175646056.2487507</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>11515775721</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>11515775721.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49889,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50073,11 @@
           <t>94.3</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>106.92</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>103.14</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>106.92</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>103.14</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50124,16 @@
           <t>3032171594.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>3191641823.4</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>3191641823.4</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>3527299622.7</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>7285669264.58</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>7285669264.58</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50150,10 @@
           <t>-477849918.1702256</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>3032171594</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>3032171594.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50319,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50503,11 @@
           <t>95.85999999999999</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>108.02</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>102.75</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>108.02</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>102.75</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50554,16 @@
           <t>3089667541.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>4058514408.6</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>4058514408.6</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>3531039856.9</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>7317342463.3</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>7317342463.3</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50580,10 @@
           <t>-485391942.3698263</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>3089667541</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>3089667541.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50749,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50933,11 @@
           <t>98.74</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>109.04</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>102.19</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>109.04</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>102.19</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50984,16 @@
           <t>2778009293.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>4453509900.0</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>4453509900</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>3688316666.2</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>7280178623.2</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>7280178623.2</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51010,10 @@
           <t>-484991116.1774759</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>2778009293</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>2778009293.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51179,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51363,11 @@
           <t>101.34</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>110.06</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>101.66</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>110.06</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>101.66</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51414,16 @@
           <t>3068959808.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>4175037440.4</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>4175037440.4</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>3901577638.9</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>7265450343.64</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>7265450343.64</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51440,10 @@
           <t>-433705440.8963513</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>3068959808</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>3068959808.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51609,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51793,11 @@
           <t>103.48</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>111.34</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>101.12</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>111.34</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>101.12</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51844,16 @@
           <t>3989400881.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>3985238440.6</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>3985238440.6</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>3979054603.6</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>7220968787.64</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>7220968787.64</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51870,10 @@
           <t>-376123979.9270172</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>3989400881</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>3989400881.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52039,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52223,11 @@
           <t>105.36</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>111.96</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>100.52</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>111.96</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>100.52</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52274,16 @@
           <t>7366534520.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>3862957422.0</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>3862957422</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>4011436058.8</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>7171595467.56</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>7171595467.56</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52300,10 @@
           <t>-379050437.0805759</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>7366534520</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>7366534520.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52469,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52653,11 @@
           <t>107.2</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>112.52</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>99.87</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>112.52</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>99.87</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52704,16 @@
           <t>5064644998.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>3003565305.2</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>3003565305.2</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>4108066698.5</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>7070679471.22</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>7070679471.22</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52730,10 @@
           <t>-731529321.5827818</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>5064644998</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>5064644998.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
@@ -53629,7 +52899,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -53813,15 +53083,11 @@
           <t>107.6</t>
         </is>
       </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>112.4</t>
-        </is>
-      </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>99.02</t>
-        </is>
+      <c r="AM123" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>99.02</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -53868,20 +53134,16 @@
           <t>1385646995.0</t>
         </is>
       </c>
-      <c r="AX123" t="inlineStr">
-        <is>
-          <t>2923123432.4</t>
-        </is>
+      <c r="AX123" t="n">
+        <v>2923123432.4</v>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
           <t>4157974302.6</t>
         </is>
       </c>
-      <c r="AZ123" t="inlineStr">
-        <is>
-          <t>7004676232.68</t>
-        </is>
+      <c r="AZ123" t="n">
+        <v>7004676232.68</v>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
@@ -53898,8 +53160,10 @@
           <t>-962313517.7436905</t>
         </is>
       </c>
-      <c r="BD123" t="n">
-        <v>1385646995</v>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>1385646995.0</t>
+        </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
@@ -54065,7 +53329,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -54249,15 +53513,11 @@
           <t>164.2</t>
         </is>
       </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>176.35</t>
-        </is>
-      </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>178.66</t>
-        </is>
+      <c r="AM124" t="n">
+        <v>176.35</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>178.66</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -54304,20 +53564,16 @@
           <t>237989780.0</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>367839281.4</t>
-        </is>
+      <c r="AX124" t="n">
+        <v>367839281.4</v>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
           <t>390785616.2</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
-        <is>
-          <t>619088599.9</t>
-        </is>
+      <c r="AZ124" t="n">
+        <v>619088599.9</v>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
@@ -54334,8 +53590,10 @@
           <t>-136007795.8903053</t>
         </is>
       </c>
-      <c r="BD124" t="n">
-        <v>237989780</v>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>237989780.0</t>
+        </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
@@ -54501,7 +53759,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -54685,15 +53943,11 @@
           <t>163.3</t>
         </is>
       </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>176.75</t>
-        </is>
-      </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>179.19</t>
-        </is>
+      <c r="AM125" t="n">
+        <v>176.75</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>179.19</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -54740,20 +53994,16 @@
           <t>159879057.0</t>
         </is>
       </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>390309422.8</t>
-        </is>
+      <c r="AX125" t="n">
+        <v>390309422.8</v>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
           <t>388711962.0</t>
         </is>
       </c>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>624204896.68</t>
-        </is>
+      <c r="AZ125" t="n">
+        <v>624204896.6799999</v>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
@@ -54770,8 +54020,10 @@
           <t>-136759988.5246557</t>
         </is>
       </c>
-      <c r="BD125" t="n">
-        <v>159879057</v>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>159879057.0</t>
+        </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
@@ -54937,7 +54189,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -55121,15 +54373,11 @@
           <t>163.2</t>
         </is>
       </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>177.4</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>179.87</t>
-        </is>
+      <c r="AM126" t="n">
+        <v>177.4</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>179.87</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -55176,20 +54424,16 @@
           <t>281592910.0</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>454120103.0</t>
-        </is>
+      <c r="AX126" t="n">
+        <v>454120103</v>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
           <t>408623891.0</t>
         </is>
       </c>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>634139495.34</t>
-        </is>
+      <c r="AZ126" t="n">
+        <v>634139495.34</v>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
@@ -55206,8 +54450,10 @@
           <t>-124581258.0907041</t>
         </is>
       </c>
-      <c r="BD126" t="n">
-        <v>281592910</v>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>281592910.0</t>
+        </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
@@ -55373,7 +54619,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -55557,15 +54803,11 @@
           <t>164.2</t>
         </is>
       </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>178.15</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>180.47</t>
-        </is>
+      <c r="AM127" t="n">
+        <v>178.15</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>180.47</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -55612,20 +54854,16 @@
           <t>661439743.0</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>465917519.0</t>
-        </is>
+      <c r="AX127" t="n">
+        <v>465917519</v>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
           <t>425236210.1</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>640116204.56</t>
-        </is>
+      <c r="AZ127" t="n">
+        <v>640116204.5599999</v>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
@@ -55642,8 +54880,10 @@
           <t>-115774511.0746768</t>
         </is>
       </c>
-      <c r="BD127" t="n">
-        <v>661439743</v>
+      <c r="BD127" t="inlineStr">
+        <is>
+          <t>661439743.0</t>
+        </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
@@ -55809,7 +55049,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -55993,15 +55233,11 @@
           <t>165.8</t>
         </is>
       </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>178.8</t>
-        </is>
-      </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>181.02</t>
-        </is>
+      <c r="AM128" t="n">
+        <v>178.8</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>181.02</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -56048,20 +55284,16 @@
           <t>498294917.0</t>
         </is>
       </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>454526412.0</t>
-        </is>
+      <c r="AX128" t="n">
+        <v>454526412</v>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
           <t>417725808.9</t>
         </is>
       </c>
-      <c r="AZ128" t="inlineStr">
-        <is>
-          <t>631196639.66</t>
-        </is>
+      <c r="AZ128" t="n">
+        <v>631196639.66</v>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
@@ -56078,8 +55310,10 @@
           <t>-139756514.9062564</t>
         </is>
       </c>
-      <c r="BD128" t="n">
-        <v>498294917</v>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>498294917.0</t>
+        </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
@@ -56245,7 +55479,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -56429,15 +55663,11 @@
           <t>167.8</t>
         </is>
       </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>179.3</t>
-        </is>
-      </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>181.48</t>
-        </is>
+      <c r="AM129" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>181.48</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -56484,20 +55714,16 @@
           <t>350340487.0</t>
         </is>
       </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>413731951.0</t>
-        </is>
+      <c r="AX129" t="n">
+        <v>413731951</v>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
           <t>411216325.6</t>
         </is>
       </c>
-      <c r="AZ129" t="inlineStr">
-        <is>
-          <t>634370543.96</t>
-        </is>
+      <c r="AZ129" t="n">
+        <v>634370543.96</v>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
@@ -56514,8 +55740,10 @@
           <t>-151545413.4904325</t>
         </is>
       </c>
-      <c r="BD129" t="n">
-        <v>350340487</v>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>350340487.0</t>
+        </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
@@ -56681,7 +55909,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -56865,15 +56093,11 @@
           <t>170.7</t>
         </is>
       </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>179.98</t>
-        </is>
-      </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>182.09</t>
-        </is>
+      <c r="AM130" t="n">
+        <v>179.98</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>182.09</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -56920,20 +56144,16 @@
           <t>478932458.0</t>
         </is>
       </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>387114501.2</t>
-        </is>
+      <c r="AX130" t="n">
+        <v>387114501.2</v>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
           <t>473719052.0</t>
         </is>
       </c>
-      <c r="AZ130" t="inlineStr">
-        <is>
-          <t>647350541.68</t>
-        </is>
+      <c r="AZ130" t="n">
+        <v>647350541.6799999</v>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
@@ -56950,8 +56170,10 @@
           <t>-147122100.6288829</t>
         </is>
       </c>
-      <c r="BD130" t="n">
-        <v>478932458</v>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>478932458.0</t>
+        </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
@@ -57117,7 +56339,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -57301,15 +56523,11 @@
           <t>173.6</t>
         </is>
       </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>180.65</t>
-        </is>
-      </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>182.55</t>
-        </is>
+      <c r="AM131" t="n">
+        <v>180.65</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>182.55</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -57356,20 +56574,16 @@
           <t>340579990.0</t>
         </is>
       </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>363127679.0</t>
-        </is>
+      <c r="AX131" t="n">
+        <v>363127679</v>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
           <t>670451790.8</t>
         </is>
       </c>
-      <c r="AZ131" t="inlineStr">
-        <is>
-          <t>644918717.5</t>
-        </is>
+      <c r="AZ131" t="n">
+        <v>644918717.5</v>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
@@ -57386,8 +56600,10 @@
           <t>-149326432.6970662</t>
         </is>
       </c>
-      <c r="BD131" t="n">
-        <v>340579990</v>
+      <c r="BD131" t="inlineStr">
+        <is>
+          <t>340579990.0</t>
+        </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
@@ -57553,7 +56769,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -57737,15 +56953,11 @@
           <t>175.7</t>
         </is>
       </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>181.12</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>182.92</t>
-        </is>
+      <c r="AM132" t="n">
+        <v>181.12</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>182.92</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -57792,20 +57004,16 @@
           <t>604484208.0</t>
         </is>
       </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>384554901.2</t>
-        </is>
+      <c r="AX132" t="n">
+        <v>384554901.2</v>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
           <t>1377596235.0</t>
         </is>
       </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>654170853.0</t>
-        </is>
+      <c r="AZ132" t="n">
+        <v>654170853</v>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
@@ -57822,8 +57030,10 @@
           <t>-132318912.9124327</t>
         </is>
       </c>
-      <c r="BD132" t="n">
-        <v>604484208</v>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>604484208.0</t>
+        </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
@@ -57989,7 +57199,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -58173,15 +57383,11 @@
           <t>177.8</t>
         </is>
       </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>181.55</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>183.34</t>
-        </is>
+      <c r="AM133" t="n">
+        <v>181.55</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>183.34</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -58228,20 +57434,16 @@
           <t>294322612.0</t>
         </is>
       </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>380925205.8</t>
-        </is>
+      <c r="AX133" t="n">
+        <v>380925205.8</v>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
           <t>1777576263.3</t>
         </is>
       </c>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>698405618.96</t>
-        </is>
+      <c r="AZ133" t="n">
+        <v>698405618.96</v>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
@@ -58258,8 +57460,10 @@
           <t>-131572232.5446552</t>
         </is>
       </c>
-      <c r="BD133" t="n">
-        <v>294322612</v>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>294322612.0</t>
+        </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
@@ -58425,7 +57629,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -58609,15 +57813,11 @@
           <t>179.8</t>
         </is>
       </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>181.42</t>
-        </is>
-      </c>
-      <c r="AN134" t="inlineStr">
-        <is>
-          <t>183.81</t>
-        </is>
+      <c r="AM134" t="n">
+        <v>181.42</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>183.81</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
@@ -58664,20 +57864,16 @@
           <t>217253238.0</t>
         </is>
       </c>
-      <c r="AX134" t="inlineStr">
-        <is>
-          <t>408700700.2</t>
-        </is>
+      <c r="AX134" t="n">
+        <v>408700700.2</v>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
           <t>1872522206.7</t>
         </is>
       </c>
-      <c r="AZ134" t="inlineStr">
-        <is>
-          <t>746966653.34</t>
-        </is>
+      <c r="AZ134" t="n">
+        <v>746966653.34</v>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
@@ -58694,8 +57890,10 @@
           <t>-92574938.4283781</t>
         </is>
       </c>
-      <c r="BD134" t="n">
-        <v>217253238</v>
+      <c r="BD134" t="inlineStr">
+        <is>
+          <t>217253238.0</t>
+        </is>
       </c>
       <c r="BE134" t="inlineStr">
         <is>
